--- a/Test Hardware/980HX-8880F5-KBG-A10/F5_PowerUpdates/F5_ChannelAssignment.xlsx
+++ b/Test Hardware/980HX-8880F5-KBG-A10/F5_PowerUpdates/F5_ChannelAssignment.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\iTest\homeoffice\Test Hardware\980HX-8880F5-KBG-A10\F5_PowerUpdates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02B5B8A-B0D2-4157-8F95-5A2B242D3007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721F6067-B4DE-4E62-83C5-913FC5742562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="615" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TX_RX" sheetId="1" r:id="rId1"/>
-    <sheet name="Power" sheetId="2" r:id="rId2"/>
-    <sheet name="L11" sheetId="3" r:id="rId3"/>
-    <sheet name="L13" sheetId="4" r:id="rId4"/>
+    <sheet name="L11" sheetId="3" r:id="rId2"/>
+    <sheet name="L13" sheetId="4" r:id="rId3"/>
+    <sheet name="L15" sheetId="5" r:id="rId4"/>
+    <sheet name="L20" sheetId="6" r:id="rId5"/>
+    <sheet name="L22" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="964">
   <si>
     <t>S1_Rx_85Dch004-</t>
   </si>
@@ -2103,12 +2105,6 @@
     <t>D11502</t>
   </si>
   <si>
-    <t>S1_DPS_F_003</t>
-  </si>
-  <si>
-    <t>S1_DPS_F_002</t>
-  </si>
-  <si>
     <t>S1_DPS_F_009</t>
   </si>
   <si>
@@ -2181,48 +2177,12 @@
     <t>S4_DPS_F_009</t>
   </si>
   <si>
-    <t>S3_DPS_F_002</t>
-  </si>
-  <si>
-    <t>S2_DPS_F_002</t>
-  </si>
-  <si>
-    <t>S4_DPS_F_002</t>
-  </si>
-  <si>
-    <t>S3_DPS_F_001</t>
-  </si>
-  <si>
-    <t>S1_DPS_F_001</t>
-  </si>
-  <si>
-    <t>S2_DPS_F_001</t>
-  </si>
-  <si>
-    <t>S4_DPS_F_001</t>
-  </si>
-  <si>
     <t>S3_DPS_F_013</t>
   </si>
   <si>
     <t>S1_DPS_F_013</t>
   </si>
   <si>
-    <t>S2_DPS_F_013</t>
-  </si>
-  <si>
-    <t>S4_DPS_F_013</t>
-  </si>
-  <si>
-    <t>S3_DPS_F_003</t>
-  </si>
-  <si>
-    <t>S2_DPS_F_003</t>
-  </si>
-  <si>
-    <t>S4_DPS_F_003</t>
-  </si>
-  <si>
     <t>S3_DPS_F_007</t>
   </si>
   <si>
@@ -2283,15 +2243,9 @@
     <t>S2_M_DPS_F_003</t>
   </si>
   <si>
-    <t>CSDPS225P9</t>
-  </si>
-  <si>
     <t>CSDPS225P10</t>
   </si>
   <si>
-    <t>CSDPS225P11</t>
-  </si>
-  <si>
     <t>S4_M_DPS_F_002</t>
   </si>
   <si>
@@ -2307,9 +2261,6 @@
     <t>CSDPS425P11</t>
   </si>
   <si>
-    <t>CSDPS425P1</t>
-  </si>
-  <si>
     <t>CSDPS429P13</t>
   </si>
   <si>
@@ -2385,18 +2336,6 @@
     <t>CSDPS429P2</t>
   </si>
   <si>
-    <t>CSDPS225P15</t>
-  </si>
-  <si>
-    <t>CSDPS425P14</t>
-  </si>
-  <si>
-    <t>CSDPS225P7</t>
-  </si>
-  <si>
-    <t>CSDPS425P8</t>
-  </si>
-  <si>
     <t>CSDPS425P2</t>
   </si>
   <si>
@@ -2406,21 +2345,9 @@
     <t>CSDPS229P13</t>
   </si>
   <si>
-    <t>CSDPS429P12</t>
-  </si>
-  <si>
-    <t>CSDPS229P5</t>
-  </si>
-  <si>
-    <t>CSDPS429P6</t>
-  </si>
-  <si>
     <t>CSDPS425P7</t>
   </si>
   <si>
-    <t>CSDPS425P6</t>
-  </si>
-  <si>
     <t>CSDPS225P4</t>
   </si>
   <si>
@@ -2430,15 +2357,9 @@
     <t>S3_DPS_F_005</t>
   </si>
   <si>
-    <t>CSDPS429P14</t>
-  </si>
-  <si>
     <t>S3_DPS_F_004</t>
   </si>
   <si>
-    <t>CSDPS229P15</t>
-  </si>
-  <si>
     <t>CSDPS429P8</t>
   </si>
   <si>
@@ -2454,36 +2375,9 @@
     <t>S1_DPS_F_004</t>
   </si>
   <si>
-    <t>CSDPS229P3</t>
-  </si>
-  <si>
     <t>CSDPS425P16</t>
   </si>
   <si>
-    <t>CSDPS425P12</t>
-  </si>
-  <si>
-    <t>S4_DPS_F_004</t>
-  </si>
-  <si>
-    <t>CSDPS425P4</t>
-  </si>
-  <si>
-    <t>S2_DPS_F_005</t>
-  </si>
-  <si>
-    <t>CSDPS225P13</t>
-  </si>
-  <si>
-    <t>S2_DPS_F_004</t>
-  </si>
-  <si>
-    <t>CSDPS225P5</t>
-  </si>
-  <si>
-    <t>S4_DPS_F_005</t>
-  </si>
-  <si>
     <t>CSDPS225P2</t>
   </si>
   <si>
@@ -2598,15 +2492,9 @@
     <t>S2_M_DPS_FS_001</t>
   </si>
   <si>
-    <t>CSDPS225PS9</t>
-  </si>
-  <si>
     <t>S2_M_DPS_GS_001</t>
   </si>
   <si>
-    <t>CSDPS225GS9</t>
-  </si>
-  <si>
     <t>S2_M_DPS_FS_002</t>
   </si>
   <si>
@@ -2622,15 +2510,9 @@
     <t>S2_M_DPS_FS_003</t>
   </si>
   <si>
-    <t>CSDPS225PS11</t>
-  </si>
-  <si>
     <t>S2_M_DPS_GS_003</t>
   </si>
   <si>
-    <t>CSDPS225GS11</t>
-  </si>
-  <si>
     <t>S4_M_DPS_FS_001</t>
   </si>
   <si>
@@ -2670,15 +2552,9 @@
     <t>S4_DPS_FS_007</t>
   </si>
   <si>
-    <t>CSDPS425PS1</t>
-  </si>
-  <si>
     <t>S4_DPS_GS_007</t>
   </si>
   <si>
-    <t>CSDPS425GS1</t>
-  </si>
-  <si>
     <t>S3_DPS_FS_011</t>
   </si>
   <si>
@@ -2907,15 +2783,9 @@
     <t>CSDPS229GS8</t>
   </si>
   <si>
-    <t>S1_DPS_FS_001</t>
-  </si>
-  <si>
     <t>CSDPS429PS7</t>
   </si>
   <si>
-    <t>S1_DPS_GS_001</t>
-  </si>
-  <si>
     <t>CSDPS429GS7</t>
   </si>
   <si>
@@ -2931,66 +2801,24 @@
     <t>CSDPS229GS1</t>
   </si>
   <si>
-    <t>S3_DPS_FS_001</t>
-  </si>
-  <si>
     <t>CSDPS429PS2</t>
   </si>
   <si>
-    <t>S3_DPS_GS_001</t>
-  </si>
-  <si>
     <t>CSDPS429GS2</t>
   </si>
   <si>
     <t>S2_DPS_FS_010</t>
   </si>
   <si>
-    <t>CSDPS225PS15</t>
-  </si>
-  <si>
     <t>S2_DPS_GS_010</t>
   </si>
   <si>
-    <t>CSDPS225GS15</t>
-  </si>
-  <si>
-    <t>S2_DPS_FS_001</t>
-  </si>
-  <si>
-    <t>CSDPS425PS14</t>
-  </si>
-  <si>
-    <t>S2_DPS_GS_001</t>
-  </si>
-  <si>
-    <t>CSDPS425GS14</t>
-  </si>
-  <si>
     <t>S2_DPS_FS_009</t>
   </si>
   <si>
-    <t>CSDPS225PS7</t>
-  </si>
-  <si>
     <t>S2_DPS_GS_009</t>
   </si>
   <si>
-    <t>CSDPS225GS7</t>
-  </si>
-  <si>
-    <t>S4_DPS_FS_001</t>
-  </si>
-  <si>
-    <t>CSDPS425PS8</t>
-  </si>
-  <si>
-    <t>S4_DPS_GS_001</t>
-  </si>
-  <si>
-    <t>CSDPS425GS8</t>
-  </si>
-  <si>
     <t>S4_DPS_FS_009</t>
   </si>
   <si>
@@ -3018,27 +2846,15 @@
     <t>S3_DPS_FS_005</t>
   </si>
   <si>
-    <t>CSDPS429PS14</t>
-  </si>
-  <si>
     <t>S3_DPS_GS_005</t>
   </si>
   <si>
-    <t>CSDPS429GS14</t>
-  </si>
-  <si>
     <t>S3_DPS_FS_004</t>
   </si>
   <si>
-    <t>CSDPS229PS15</t>
-  </si>
-  <si>
     <t>S3_DPS_GS_004</t>
   </si>
   <si>
-    <t>CSDPS229GS15</t>
-  </si>
-  <si>
     <t>S1_DPS_FS_013</t>
   </si>
   <si>
@@ -3078,178 +2894,40 @@
     <t>S1_DPS_FS_004</t>
   </si>
   <si>
-    <t>CSDPS229PS3</t>
-  </si>
-  <si>
     <t>S1_DPS_GS_004</t>
   </si>
   <si>
-    <t>CSDPS229GS3</t>
-  </si>
-  <si>
-    <t>S4_DPS_FS_013</t>
-  </si>
-  <si>
     <t>CSDPS425PS16</t>
   </si>
   <si>
-    <t>S4_DPS_GS_013</t>
-  </si>
-  <si>
     <t>CSDPS425GS16</t>
   </si>
   <si>
-    <t>S2_DPS_FS_013</t>
-  </si>
-  <si>
-    <t>CSDPS425PS12</t>
-  </si>
-  <si>
-    <t>S2_DPS_GS_013</t>
-  </si>
-  <si>
-    <t>CSDPS425GS12</t>
-  </si>
-  <si>
-    <t>S4_DPS_FS_004</t>
-  </si>
-  <si>
-    <t>CSDPS425PS4</t>
-  </si>
-  <si>
-    <t>S4_DPS_GS_004</t>
-  </si>
-  <si>
-    <t>CSDPS425GS4</t>
-  </si>
-  <si>
-    <t>S2_DPS_FS_005</t>
-  </si>
-  <si>
-    <t>CSDPS225PS13</t>
-  </si>
-  <si>
-    <t>S2_DPS_GS_005</t>
-  </si>
-  <si>
-    <t>CSDPS225GS13</t>
-  </si>
-  <si>
-    <t>S2_DPS_FS_004</t>
-  </si>
-  <si>
-    <t>CSDPS225PS5</t>
-  </si>
-  <si>
-    <t>S2_DPS_GS_004</t>
-  </si>
-  <si>
-    <t>CSDPS225GS5</t>
-  </si>
-  <si>
-    <t>S4_DPS_FS_005</t>
-  </si>
-  <si>
     <t>CSDPS225PS2</t>
   </si>
   <si>
-    <t>S4_DPS_GS_005</t>
-  </si>
-  <si>
     <t>CSDPS225GS2</t>
   </si>
   <si>
-    <t>S1_DPS_FS_003</t>
-  </si>
-  <si>
     <t>CSDPS229PS13</t>
   </si>
   <si>
-    <t>S1_DPS_GS_003</t>
-  </si>
-  <si>
     <t>CSDPS229GS13</t>
   </si>
   <si>
-    <t>S3_DPS_FS_002</t>
-  </si>
-  <si>
-    <t>CSDPS429PS12</t>
-  </si>
-  <si>
-    <t>S3_DPS_GS_002</t>
-  </si>
-  <si>
-    <t>CSDPS429GS12</t>
-  </si>
-  <si>
-    <t>S1_DPS_FS_002</t>
-  </si>
-  <si>
-    <t>CSDPS229PS5</t>
-  </si>
-  <si>
-    <t>S1_DPS_GS_002</t>
-  </si>
-  <si>
-    <t>CSDPS229GS5</t>
-  </si>
-  <si>
-    <t>S3_DPS_FS_003</t>
-  </si>
-  <si>
-    <t>CSDPS429PS6</t>
-  </si>
-  <si>
-    <t>S3_DPS_GS_003</t>
-  </si>
-  <si>
-    <t>CSDPS429GS6</t>
-  </si>
-  <si>
-    <t>S4_DPS_FS_002</t>
-  </si>
-  <si>
     <t>CSDPS425PS7</t>
   </si>
   <si>
-    <t>S4_DPS_GS_002</t>
-  </si>
-  <si>
     <t>CSDPS425GS7</t>
   </si>
   <si>
-    <t>S4_DPS_FS_003</t>
-  </si>
-  <si>
-    <t>CSDPS425PS6</t>
-  </si>
-  <si>
-    <t>S4_DPS_GS_003</t>
-  </si>
-  <si>
-    <t>CSDPS425GS6</t>
-  </si>
-  <si>
-    <t>S2_DPS_FS_003</t>
-  </si>
-  <si>
     <t>CSDPS225PS4</t>
   </si>
   <si>
-    <t>S2_DPS_GS_003</t>
-  </si>
-  <si>
     <t>CSDPS225GS4</t>
   </si>
   <si>
-    <t>S2_DPS_FS_002</t>
-  </si>
-  <si>
     <t>CSDPS225PS3</t>
-  </si>
-  <si>
-    <t>S2_DPS_GS_002</t>
   </si>
   <si>
     <t>CSDPS225GS3</t>
@@ -3592,13 +3270,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B344"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" spans="1:2" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3606,7 +3284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75">
+    <row r="2" spans="1:2" ht="15.6">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3614,7 +3292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75">
+    <row r="3" spans="1:2" ht="15.6">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3622,7 +3300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75">
+    <row r="4" spans="1:2" ht="15.6">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3630,7 +3308,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75">
+    <row r="5" spans="1:2" ht="15.6">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -3638,7 +3316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75">
+    <row r="6" spans="1:2" ht="15.6">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -3646,7 +3324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75">
+    <row r="7" spans="1:2" ht="15.6">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -3654,7 +3332,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75">
+    <row r="8" spans="1:2" ht="15.6">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -3662,7 +3340,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75">
+    <row r="9" spans="1:2" ht="15.6">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -3670,7 +3348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75">
+    <row r="10" spans="1:2" ht="15.6">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3678,7 +3356,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75">
+    <row r="11" spans="1:2" ht="15.6">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -3686,7 +3364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75">
+    <row r="12" spans="1:2" ht="15.6">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -3694,7 +3372,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75">
+    <row r="13" spans="1:2" ht="15.6">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -3702,7 +3380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75">
+    <row r="14" spans="1:2" ht="15.6">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -3710,7 +3388,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75">
+    <row r="15" spans="1:2" ht="15.6">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -3718,7 +3396,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75">
+    <row r="16" spans="1:2" ht="15.6">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -3726,7 +3404,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75">
+    <row r="17" spans="1:2" ht="15.6">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -3734,7 +3412,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75">
+    <row r="18" spans="1:2" ht="15.6">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -3742,7 +3420,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75">
+    <row r="19" spans="1:2" ht="15.6">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -3750,7 +3428,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75">
+    <row r="20" spans="1:2" ht="15.6">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -3758,7 +3436,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75">
+    <row r="21" spans="1:2" ht="15.6">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -3766,7 +3444,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75">
+    <row r="22" spans="1:2" ht="15.6">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -3774,7 +3452,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75">
+    <row r="23" spans="1:2" ht="15.6">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
@@ -3782,7 +3460,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75">
+    <row r="24" spans="1:2" ht="15.6">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -3790,7 +3468,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75">
+    <row r="25" spans="1:2" ht="15.6">
       <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
@@ -3798,7 +3476,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75">
+    <row r="26" spans="1:2" ht="15.6">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -3806,7 +3484,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75">
+    <row r="27" spans="1:2" ht="15.6">
       <c r="A27" s="1" t="s">
         <v>52</v>
       </c>
@@ -3814,7 +3492,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75">
+    <row r="28" spans="1:2" ht="15.6">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -3822,7 +3500,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75">
+    <row r="29" spans="1:2" ht="15.6">
       <c r="A29" s="1" t="s">
         <v>56</v>
       </c>
@@ -3830,7 +3508,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75">
+    <row r="30" spans="1:2" ht="15.6">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -3838,7 +3516,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75">
+    <row r="31" spans="1:2" ht="15.6">
       <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
@@ -3846,7 +3524,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75">
+    <row r="32" spans="1:2" ht="15.6">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -3854,7 +3532,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75">
+    <row r="33" spans="1:2" ht="15.6">
       <c r="A33" s="1" t="s">
         <v>64</v>
       </c>
@@ -3862,7 +3540,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75">
+    <row r="34" spans="1:2" ht="15.6">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -3870,7 +3548,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75">
+    <row r="35" spans="1:2" ht="15.6">
       <c r="A35" s="1" t="s">
         <v>68</v>
       </c>
@@ -3878,7 +3556,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75">
+    <row r="36" spans="1:2" ht="15.6">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -3886,7 +3564,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75">
+    <row r="37" spans="1:2" ht="15.6">
       <c r="A37" s="1" t="s">
         <v>72</v>
       </c>
@@ -3894,7 +3572,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75">
+    <row r="38" spans="1:2" ht="15.6">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -3902,7 +3580,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75">
+    <row r="39" spans="1:2" ht="15.6">
       <c r="A39" s="1" t="s">
         <v>76</v>
       </c>
@@ -3910,7 +3588,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75">
+    <row r="40" spans="1:2" ht="15.6">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -3918,7 +3596,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75">
+    <row r="41" spans="1:2" ht="15.6">
       <c r="A41" s="1" t="s">
         <v>80</v>
       </c>
@@ -3926,7 +3604,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75">
+    <row r="42" spans="1:2" ht="15.6">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -3934,7 +3612,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75">
+    <row r="43" spans="1:2" ht="15.6">
       <c r="A43" s="1" t="s">
         <v>84</v>
       </c>
@@ -3942,7 +3620,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75">
+    <row r="44" spans="1:2" ht="15.6">
       <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
@@ -3950,7 +3628,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75">
+    <row r="45" spans="1:2" ht="15.6">
       <c r="A45" s="1" t="s">
         <v>88</v>
       </c>
@@ -3958,7 +3636,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75">
+    <row r="46" spans="1:2" ht="15.6">
       <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
@@ -3966,7 +3644,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75">
+    <row r="47" spans="1:2" ht="15.6">
       <c r="A47" s="1" t="s">
         <v>92</v>
       </c>
@@ -3974,7 +3652,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75">
+    <row r="48" spans="1:2" ht="15.6">
       <c r="A48" s="1" t="s">
         <v>94</v>
       </c>
@@ -3982,7 +3660,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75">
+    <row r="49" spans="1:2" ht="15.6">
       <c r="A49" s="1" t="s">
         <v>96</v>
       </c>
@@ -3990,7 +3668,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75">
+    <row r="50" spans="1:2" ht="15.6">
       <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
@@ -3998,7 +3676,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75">
+    <row r="51" spans="1:2" ht="15.6">
       <c r="A51" s="1" t="s">
         <v>100</v>
       </c>
@@ -4006,7 +3684,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75">
+    <row r="52" spans="1:2" ht="15.6">
       <c r="A52" s="1" t="s">
         <v>102</v>
       </c>
@@ -4014,7 +3692,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75">
+    <row r="53" spans="1:2" ht="15.6">
       <c r="A53" s="1" t="s">
         <v>104</v>
       </c>
@@ -4022,7 +3700,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75">
+    <row r="54" spans="1:2" ht="15.6">
       <c r="A54" s="1" t="s">
         <v>106</v>
       </c>
@@ -4030,7 +3708,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75">
+    <row r="55" spans="1:2" ht="15.6">
       <c r="A55" s="1" t="s">
         <v>108</v>
       </c>
@@ -4038,7 +3716,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75">
+    <row r="56" spans="1:2" ht="15.6">
       <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
@@ -4046,7 +3724,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75">
+    <row r="57" spans="1:2" ht="15.6">
       <c r="A57" s="1" t="s">
         <v>112</v>
       </c>
@@ -4054,7 +3732,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75">
+    <row r="58" spans="1:2" ht="15.6">
       <c r="A58" s="1" t="s">
         <v>114</v>
       </c>
@@ -4062,7 +3740,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75">
+    <row r="59" spans="1:2" ht="15.6">
       <c r="A59" s="1" t="s">
         <v>116</v>
       </c>
@@ -4070,7 +3748,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75">
+    <row r="60" spans="1:2" ht="15.6">
       <c r="A60" s="1" t="s">
         <v>118</v>
       </c>
@@ -4078,7 +3756,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75">
+    <row r="61" spans="1:2" ht="15.6">
       <c r="A61" s="1" t="s">
         <v>120</v>
       </c>
@@ -4086,7 +3764,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75">
+    <row r="62" spans="1:2" ht="15.6">
       <c r="A62" s="1" t="s">
         <v>122</v>
       </c>
@@ -4094,7 +3772,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75">
+    <row r="63" spans="1:2" ht="15.6">
       <c r="A63" s="1" t="s">
         <v>124</v>
       </c>
@@ -4102,7 +3780,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75">
+    <row r="64" spans="1:2" ht="15.6">
       <c r="A64" s="1" t="s">
         <v>126</v>
       </c>
@@ -4110,7 +3788,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75">
+    <row r="65" spans="1:2" ht="15.6">
       <c r="A65" s="1" t="s">
         <v>128</v>
       </c>
@@ -4118,7 +3796,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75">
+    <row r="66" spans="1:2" ht="15.6">
       <c r="A66" s="1" t="s">
         <v>130</v>
       </c>
@@ -4126,7 +3804,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75">
+    <row r="67" spans="1:2" ht="15.6">
       <c r="A67" s="1" t="s">
         <v>132</v>
       </c>
@@ -4134,7 +3812,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75">
+    <row r="68" spans="1:2" ht="15.6">
       <c r="A68" s="1" t="s">
         <v>134</v>
       </c>
@@ -4142,7 +3820,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75">
+    <row r="69" spans="1:2" ht="15.6">
       <c r="A69" s="1" t="s">
         <v>136</v>
       </c>
@@ -4150,7 +3828,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75">
+    <row r="70" spans="1:2" ht="15.6">
       <c r="A70" s="1" t="s">
         <v>138</v>
       </c>
@@ -4158,7 +3836,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75">
+    <row r="71" spans="1:2" ht="15.6">
       <c r="A71" s="1" t="s">
         <v>140</v>
       </c>
@@ -4166,7 +3844,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75">
+    <row r="72" spans="1:2" ht="15.6">
       <c r="A72" s="1" t="s">
         <v>142</v>
       </c>
@@ -4174,7 +3852,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75">
+    <row r="73" spans="1:2" ht="15.6">
       <c r="A73" s="1" t="s">
         <v>144</v>
       </c>
@@ -4182,7 +3860,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75">
+    <row r="74" spans="1:2" ht="15.6">
       <c r="A74" s="1" t="s">
         <v>146</v>
       </c>
@@ -4190,7 +3868,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75">
+    <row r="75" spans="1:2" ht="15.6">
       <c r="A75" s="1" t="s">
         <v>148</v>
       </c>
@@ -4198,7 +3876,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75">
+    <row r="76" spans="1:2" ht="15.6">
       <c r="A76" s="1" t="s">
         <v>150</v>
       </c>
@@ -4206,7 +3884,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75">
+    <row r="77" spans="1:2" ht="15.6">
       <c r="A77" s="1" t="s">
         <v>152</v>
       </c>
@@ -4214,7 +3892,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75">
+    <row r="78" spans="1:2" ht="15.6">
       <c r="A78" s="1" t="s">
         <v>154</v>
       </c>
@@ -4222,7 +3900,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75">
+    <row r="79" spans="1:2" ht="15.6">
       <c r="A79" s="1" t="s">
         <v>156</v>
       </c>
@@ -4230,7 +3908,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75">
+    <row r="80" spans="1:2" ht="15.6">
       <c r="A80" s="1" t="s">
         <v>158</v>
       </c>
@@ -4238,7 +3916,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75">
+    <row r="81" spans="1:2" ht="15.6">
       <c r="A81" s="1" t="s">
         <v>160</v>
       </c>
@@ -4246,7 +3924,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75">
+    <row r="82" spans="1:2" ht="15.6">
       <c r="A82" s="1" t="s">
         <v>162</v>
       </c>
@@ -4254,7 +3932,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75">
+    <row r="83" spans="1:2" ht="15.6">
       <c r="A83" s="1" t="s">
         <v>164</v>
       </c>
@@ -4262,7 +3940,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75">
+    <row r="84" spans="1:2" ht="15.6">
       <c r="A84" s="1" t="s">
         <v>166</v>
       </c>
@@ -4270,7 +3948,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75">
+    <row r="85" spans="1:2" ht="15.6">
       <c r="A85" s="1" t="s">
         <v>168</v>
       </c>
@@ -4278,7 +3956,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75">
+    <row r="86" spans="1:2" ht="15.6">
       <c r="A86" s="1" t="s">
         <v>170</v>
       </c>
@@ -4286,7 +3964,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75">
+    <row r="87" spans="1:2" ht="15.6">
       <c r="A87" s="1" t="s">
         <v>172</v>
       </c>
@@ -4294,7 +3972,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75">
+    <row r="88" spans="1:2" ht="15.6">
       <c r="A88" s="1" t="s">
         <v>174</v>
       </c>
@@ -4302,7 +3980,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75">
+    <row r="89" spans="1:2" ht="15.6">
       <c r="A89" s="1" t="s">
         <v>176</v>
       </c>
@@ -4310,7 +3988,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75">
+    <row r="90" spans="1:2" ht="15.6">
       <c r="A90" s="1" t="s">
         <v>178</v>
       </c>
@@ -4318,7 +3996,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75">
+    <row r="91" spans="1:2" ht="15.6">
       <c r="A91" s="1" t="s">
         <v>180</v>
       </c>
@@ -4326,7 +4004,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75">
+    <row r="92" spans="1:2" ht="15.6">
       <c r="A92" s="1" t="s">
         <v>182</v>
       </c>
@@ -4334,7 +4012,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75">
+    <row r="93" spans="1:2" ht="15.6">
       <c r="A93" s="1" t="s">
         <v>184</v>
       </c>
@@ -4342,7 +4020,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15.75">
+    <row r="94" spans="1:2" ht="15.6">
       <c r="A94" s="1" t="s">
         <v>186</v>
       </c>
@@ -4350,7 +4028,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75">
+    <row r="95" spans="1:2" ht="15.6">
       <c r="A95" s="1" t="s">
         <v>188</v>
       </c>
@@ -4358,7 +4036,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75">
+    <row r="96" spans="1:2" ht="15.6">
       <c r="A96" s="1" t="s">
         <v>190</v>
       </c>
@@ -4366,7 +4044,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75">
+    <row r="97" spans="1:2" ht="15.6">
       <c r="A97" s="1" t="s">
         <v>192</v>
       </c>
@@ -4374,7 +4052,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75">
+    <row r="98" spans="1:2" ht="15.6">
       <c r="A98" s="1" t="s">
         <v>194</v>
       </c>
@@ -4382,7 +4060,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75">
+    <row r="99" spans="1:2" ht="15.6">
       <c r="A99" s="1" t="s">
         <v>196</v>
       </c>
@@ -4390,7 +4068,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75">
+    <row r="100" spans="1:2" ht="15.6">
       <c r="A100" s="1" t="s">
         <v>198</v>
       </c>
@@ -4398,7 +4076,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75">
+    <row r="101" spans="1:2" ht="15.6">
       <c r="A101" s="1" t="s">
         <v>200</v>
       </c>
@@ -4406,7 +4084,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75">
+    <row r="102" spans="1:2" ht="15.6">
       <c r="A102" s="1" t="s">
         <v>202</v>
       </c>
@@ -4414,7 +4092,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15.75">
+    <row r="103" spans="1:2" ht="15.6">
       <c r="A103" s="1" t="s">
         <v>204</v>
       </c>
@@ -4422,7 +4100,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15.75">
+    <row r="104" spans="1:2" ht="15.6">
       <c r="A104" s="1" t="s">
         <v>206</v>
       </c>
@@ -4430,7 +4108,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15.75">
+    <row r="105" spans="1:2" ht="15.6">
       <c r="A105" s="1" t="s">
         <v>208</v>
       </c>
@@ -4438,7 +4116,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15.75">
+    <row r="106" spans="1:2" ht="15.6">
       <c r="A106" s="1" t="s">
         <v>210</v>
       </c>
@@ -4446,7 +4124,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15.75">
+    <row r="107" spans="1:2" ht="15.6">
       <c r="A107" s="1" t="s">
         <v>212</v>
       </c>
@@ -4454,7 +4132,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15.75">
+    <row r="108" spans="1:2" ht="15.6">
       <c r="A108" s="1" t="s">
         <v>214</v>
       </c>
@@ -4462,7 +4140,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15.75">
+    <row r="109" spans="1:2" ht="15.6">
       <c r="A109" s="1" t="s">
         <v>216</v>
       </c>
@@ -4470,7 +4148,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15.75">
+    <row r="110" spans="1:2" ht="15.6">
       <c r="A110" s="1" t="s">
         <v>218</v>
       </c>
@@ -4478,7 +4156,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15.75">
+    <row r="111" spans="1:2" ht="15.6">
       <c r="A111" s="1" t="s">
         <v>220</v>
       </c>
@@ -4486,7 +4164,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15.75">
+    <row r="112" spans="1:2" ht="15.6">
       <c r="A112" s="1" t="s">
         <v>222</v>
       </c>
@@ -4494,7 +4172,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15.75">
+    <row r="113" spans="1:2" ht="15.6">
       <c r="A113" s="1" t="s">
         <v>224</v>
       </c>
@@ -4502,7 +4180,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15.75">
+    <row r="114" spans="1:2" ht="15.6">
       <c r="A114" s="1" t="s">
         <v>226</v>
       </c>
@@ -4510,7 +4188,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15.75">
+    <row r="115" spans="1:2" ht="15.6">
       <c r="A115" s="1" t="s">
         <v>228</v>
       </c>
@@ -4518,7 +4196,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15.75">
+    <row r="116" spans="1:2" ht="15.6">
       <c r="A116" s="1" t="s">
         <v>230</v>
       </c>
@@ -4526,7 +4204,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15.75">
+    <row r="117" spans="1:2" ht="15.6">
       <c r="A117" s="1" t="s">
         <v>232</v>
       </c>
@@ -4534,7 +4212,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="15.75">
+    <row r="118" spans="1:2" ht="15.6">
       <c r="A118" s="1" t="s">
         <v>234</v>
       </c>
@@ -4542,7 +4220,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="15.75">
+    <row r="119" spans="1:2" ht="15.6">
       <c r="A119" s="1" t="s">
         <v>236</v>
       </c>
@@ -4550,7 +4228,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="15.75">
+    <row r="120" spans="1:2" ht="15.6">
       <c r="A120" s="1" t="s">
         <v>238</v>
       </c>
@@ -4558,7 +4236,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="15.75">
+    <row r="121" spans="1:2" ht="15.6">
       <c r="A121" s="1" t="s">
         <v>240</v>
       </c>
@@ -4566,7 +4244,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="15.75">
+    <row r="122" spans="1:2" ht="15.6">
       <c r="A122" s="1" t="s">
         <v>242</v>
       </c>
@@ -4574,7 +4252,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="15.75">
+    <row r="123" spans="1:2" ht="15.6">
       <c r="A123" s="1" t="s">
         <v>244</v>
       </c>
@@ -4582,7 +4260,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="15.75">
+    <row r="124" spans="1:2" ht="15.6">
       <c r="A124" s="1" t="s">
         <v>246</v>
       </c>
@@ -4590,7 +4268,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="15.75">
+    <row r="125" spans="1:2" ht="15.6">
       <c r="A125" s="1" t="s">
         <v>248</v>
       </c>
@@ -4598,7 +4276,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="15.75">
+    <row r="126" spans="1:2" ht="15.6">
       <c r="A126" s="1" t="s">
         <v>250</v>
       </c>
@@ -4606,7 +4284,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="15.75">
+    <row r="127" spans="1:2" ht="15.6">
       <c r="A127" s="1" t="s">
         <v>252</v>
       </c>
@@ -4614,7 +4292,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="15.75">
+    <row r="128" spans="1:2" ht="15.6">
       <c r="A128" s="1" t="s">
         <v>254</v>
       </c>
@@ -6356,35 +6034,39 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{068A3C14-3BD5-4B45-B74E-6069194AA1F3}">
-  <dimension ref="A1:M192"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A62C1B7-928E-4F29-88BD-9E7DDC434D58}">
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="4" t="s">
-        <v>718</v>
+      <c r="A1" s="3" t="s">
+        <v>715</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>779</v>
+        <v>729</v>
       </c>
       <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="3"/>
+      <c r="D1" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>734</v>
+      </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -6395,15 +6077,19 @@
       <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="4" t="s">
-        <v>689</v>
+      <c r="A2" s="3" t="s">
+        <v>804</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="3"/>
+      <c r="D2" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>819</v>
+      </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -6414,15 +6100,19 @@
       <c r="M2" s="3"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="4" t="s">
-        <v>688</v>
+      <c r="A3" s="3" t="s">
+        <v>806</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>788</v>
+        <v>807</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="3"/>
+      <c r="D3" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>821</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="3"/>
       <c r="H3" s="4"/>
@@ -6434,14 +6124,18 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="4" t="s">
-        <v>804</v>
+        <v>691</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>805</v>
+        <v>719</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="3"/>
+      <c r="D4" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>766</v>
+      </c>
       <c r="F4" s="4"/>
       <c r="G4" s="3"/>
       <c r="H4" s="4"/>
@@ -6453,14 +6147,18 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="4" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>802</v>
+        <v>781</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="3"/>
+      <c r="D5" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>931</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
@@ -6472,14 +6170,18 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>694</v>
+        <v>782</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>760</v>
+        <v>783</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="3"/>
+      <c r="D6" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>933</v>
+      </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="4"/>
@@ -6490,15 +6192,19 @@
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="3" t="s">
-        <v>729</v>
+      <c r="A7" s="4" t="s">
+        <v>720</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>743</v>
+        <v>722</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="3"/>
+      <c r="D7" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>779</v>
+      </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="4"/>
@@ -6509,15 +6215,19 @@
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>767</v>
+      <c r="A8" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>785</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="3"/>
+      <c r="D8" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>954</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="3"/>
       <c r="H8" s="4"/>
@@ -6528,11 +6238,17 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="3" t="s">
-        <v>690</v>
+      <c r="A9" s="4" t="s">
+        <v>786</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>780</v>
+        <v>787</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>955</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="4"/>
@@ -6541,10 +6257,16 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>778</v>
+        <v>723</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>770</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="4"/>
@@ -6553,10 +6275,16 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>700</v>
+        <v>788</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>758</v>
+        <v>789</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>962</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="4"/>
@@ -6565,10 +6293,16 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="4" t="s">
-        <v>703</v>
+        <v>790</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>770</v>
+        <v>791</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>963</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="4"/>
@@ -6577,1891 +6311,170 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="4" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>800</v>
+        <v>727</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="4" t="s">
-        <v>956</v>
+        <v>808</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>957</v>
+        <v>797</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="4" t="s">
-        <v>1048</v>
+        <v>810</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="3" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>892</v>
-      </c>
-      <c r="B19" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>840</v>
-      </c>
-      <c r="B20" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>912</v>
-      </c>
-      <c r="B21" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>960</v>
-      </c>
-      <c r="B22" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>952</v>
-      </c>
-      <c r="B23" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>884</v>
-      </c>
-      <c r="B24" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>924</v>
-      </c>
-      <c r="B25" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>958</v>
-      </c>
-      <c r="B27" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>894</v>
-      </c>
-      <c r="B32" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>842</v>
-      </c>
-      <c r="B33" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>914</v>
-      </c>
-      <c r="B34" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>962</v>
-      </c>
-      <c r="B35" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>954</v>
-      </c>
-      <c r="B36" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>886</v>
-      </c>
-      <c r="B37" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>926</v>
-      </c>
-      <c r="B38" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>693</v>
-      </c>
-      <c r="B40" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>734</v>
-      </c>
-      <c r="B41" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>735</v>
-      </c>
-      <c r="B42" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>816</v>
-      </c>
-      <c r="B43" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>820</v>
-      </c>
-      <c r="B44" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>824</v>
-      </c>
-      <c r="B45" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>818</v>
-      </c>
-      <c r="B46" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>822</v>
-      </c>
-      <c r="B47" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>826</v>
-      </c>
-      <c r="B48" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>719</v>
-      </c>
-      <c r="B49" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>715</v>
-      </c>
-      <c r="B50" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>726</v>
-      </c>
-      <c r="B51" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>812</v>
-      </c>
-      <c r="B52" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>810</v>
-      </c>
-      <c r="B53" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>695</v>
-      </c>
-      <c r="B54" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>730</v>
-      </c>
-      <c r="B55" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>775</v>
-      </c>
-      <c r="B56" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>711</v>
-      </c>
-      <c r="B57" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>710</v>
-      </c>
-      <c r="B58" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>701</v>
-      </c>
-      <c r="B59" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>705</v>
-      </c>
-      <c r="B60" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>723</v>
-      </c>
-      <c r="B61" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>972</v>
-      </c>
-      <c r="B62" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>896</v>
-      </c>
-      <c r="B67" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>848</v>
-      </c>
-      <c r="B68" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>940</v>
-      </c>
-      <c r="B69" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" t="s">
-        <v>976</v>
-      </c>
-      <c r="B70" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" t="s">
-        <v>968</v>
-      </c>
-      <c r="B71" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" t="s">
-        <v>904</v>
-      </c>
-      <c r="B72" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" t="s">
-        <v>932</v>
-      </c>
-      <c r="B73" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" t="s">
-        <v>974</v>
-      </c>
-      <c r="B75" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" t="s">
-        <v>898</v>
-      </c>
-      <c r="B80" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" t="s">
-        <v>850</v>
-      </c>
-      <c r="B81" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" t="s">
-        <v>942</v>
-      </c>
-      <c r="B82" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" t="s">
-        <v>978</v>
-      </c>
-      <c r="B83" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" t="s">
-        <v>970</v>
-      </c>
-      <c r="B84" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" t="s">
-        <v>906</v>
-      </c>
-      <c r="B85" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" t="s">
-        <v>934</v>
-      </c>
-      <c r="B86" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B87" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" t="s">
-        <v>696</v>
-      </c>
-      <c r="B88" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" t="s">
-        <v>746</v>
-      </c>
-      <c r="B89" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" t="s">
-        <v>747</v>
-      </c>
-      <c r="B90" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" t="s">
-        <v>852</v>
-      </c>
-      <c r="B91" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" t="s">
-        <v>856</v>
-      </c>
-      <c r="B92" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" t="s">
-        <v>860</v>
-      </c>
-      <c r="B93" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" t="s">
-        <v>854</v>
-      </c>
-      <c r="B94" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" t="s">
-        <v>858</v>
-      </c>
-      <c r="B95" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" t="s">
-        <v>862</v>
-      </c>
-      <c r="B96" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" t="s">
-        <v>717</v>
-      </c>
-      <c r="B97" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" t="s">
-        <v>714</v>
-      </c>
-      <c r="B98" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" t="s">
-        <v>725</v>
-      </c>
-      <c r="B99" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" t="s">
-        <v>798</v>
-      </c>
-      <c r="B100" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" t="s">
-        <v>796</v>
-      </c>
-      <c r="B101" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" t="s">
-        <v>691</v>
-      </c>
-      <c r="B102" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" t="s">
-        <v>728</v>
-      </c>
-      <c r="B103" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" t="s">
-        <v>766</v>
-      </c>
-      <c r="B104" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" t="s">
-        <v>708</v>
-      </c>
-      <c r="B105" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" t="s">
-        <v>707</v>
-      </c>
-      <c r="B106" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" t="s">
-        <v>699</v>
-      </c>
-      <c r="B107" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" t="s">
-        <v>704</v>
-      </c>
-      <c r="B108" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" t="s">
-        <v>721</v>
-      </c>
-      <c r="B109" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" t="s">
-        <v>964</v>
-      </c>
-      <c r="B110" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B111" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B112" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" t="s">
-        <v>996</v>
-      </c>
-      <c r="B113" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" t="s">
-        <v>992</v>
-      </c>
-      <c r="B114" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" t="s">
-        <v>888</v>
-      </c>
-      <c r="B115" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" t="s">
-        <v>844</v>
-      </c>
-      <c r="B116" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" t="s">
-        <v>916</v>
-      </c>
-      <c r="B117" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" t="s">
-        <v>944</v>
-      </c>
-      <c r="B118" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" t="s">
-        <v>948</v>
-      </c>
-      <c r="B119" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" t="s">
-        <v>880</v>
-      </c>
-      <c r="B120" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" t="s">
-        <v>920</v>
-      </c>
-      <c r="B121" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B122" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" t="s">
-        <v>966</v>
-      </c>
-      <c r="B123" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B124" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B125" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" t="s">
-        <v>998</v>
-      </c>
-      <c r="B126" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" t="s">
-        <v>994</v>
-      </c>
-      <c r="B127" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" t="s">
-        <v>890</v>
-      </c>
-      <c r="B128" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" t="s">
-        <v>846</v>
-      </c>
-      <c r="B129" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" t="s">
-        <v>918</v>
-      </c>
-      <c r="B130" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" t="s">
-        <v>946</v>
-      </c>
-      <c r="B131" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" t="s">
-        <v>950</v>
-      </c>
-      <c r="B132" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" t="s">
-        <v>882</v>
-      </c>
-      <c r="B133" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" t="s">
-        <v>922</v>
-      </c>
-      <c r="B134" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B135" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" t="s">
-        <v>692</v>
-      </c>
-      <c r="B136" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" t="s">
-        <v>738</v>
-      </c>
-      <c r="B137" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" t="s">
-        <v>739</v>
-      </c>
-      <c r="B138" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" t="s">
-        <v>828</v>
-      </c>
-      <c r="B139" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" t="s">
-        <v>832</v>
-      </c>
-      <c r="B140" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" t="s">
-        <v>836</v>
-      </c>
-      <c r="B141" t="s">
+      <c r="D15" s="3" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" t="s">
-        <v>830</v>
-      </c>
-      <c r="B142" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" t="s">
-        <v>834</v>
-      </c>
-      <c r="B143" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" t="s">
-        <v>838</v>
-      </c>
-      <c r="B144" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" t="s">
-        <v>720</v>
-      </c>
-      <c r="B145" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" t="s">
-        <v>716</v>
-      </c>
-      <c r="B146" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" t="s">
-        <v>727</v>
-      </c>
-      <c r="B147" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" t="s">
-        <v>808</v>
-      </c>
-      <c r="B148" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" t="s">
-        <v>814</v>
-      </c>
-      <c r="B149" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" t="s">
-        <v>697</v>
-      </c>
-      <c r="B150" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" t="s">
-        <v>731</v>
-      </c>
-      <c r="B151" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" t="s">
-        <v>771</v>
-      </c>
-      <c r="B152" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" t="s">
-        <v>713</v>
-      </c>
-      <c r="B153" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" t="s">
-        <v>712</v>
-      </c>
-      <c r="B154" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" t="s">
-        <v>702</v>
-      </c>
-      <c r="B155" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" t="s">
-        <v>706</v>
-      </c>
-      <c r="B156" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" t="s">
-        <v>724</v>
-      </c>
-      <c r="B157" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" t="s">
-        <v>980</v>
-      </c>
-      <c r="B158" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B159" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B160" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B161" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B162" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" t="s">
-        <v>900</v>
-      </c>
-      <c r="B163" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" t="s">
-        <v>876</v>
-      </c>
-      <c r="B164" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" t="s">
-        <v>928</v>
-      </c>
-      <c r="B165" t="s">
+      <c r="E15" s="3" t="s">
         <v>929</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" t="s">
-        <v>984</v>
-      </c>
-      <c r="B166" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" t="s">
-        <v>988</v>
-      </c>
-      <c r="B167" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" t="s">
-        <v>908</v>
-      </c>
-      <c r="B168" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" t="s">
-        <v>936</v>
-      </c>
-      <c r="B169" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B170" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" t="s">
-        <v>982</v>
-      </c>
-      <c r="B171" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B172" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B173" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B174" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B175" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" t="s">
-        <v>902</v>
-      </c>
-      <c r="B176" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" t="s">
-        <v>878</v>
-      </c>
-      <c r="B177" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" t="s">
-        <v>930</v>
-      </c>
-      <c r="B178" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" t="s">
-        <v>986</v>
-      </c>
-      <c r="B179" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" t="s">
-        <v>990</v>
-      </c>
-      <c r="B180" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" t="s">
-        <v>910</v>
-      </c>
-      <c r="B181" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" t="s">
-        <v>938</v>
-      </c>
-      <c r="B182" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" t="s">
-        <v>1018</v>
-      </c>
-      <c r="B183" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" t="s">
-        <v>698</v>
-      </c>
-      <c r="B184" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" t="s">
-        <v>751</v>
-      </c>
-      <c r="B185" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" t="s">
-        <v>752</v>
-      </c>
-      <c r="B186" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" t="s">
-        <v>864</v>
-      </c>
-      <c r="B187" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" t="s">
-        <v>868</v>
-      </c>
-      <c r="B188" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" t="s">
-        <v>872</v>
-      </c>
-      <c r="B189" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" t="s">
-        <v>866</v>
-      </c>
-      <c r="B190" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" t="s">
-        <v>870</v>
-      </c>
-      <c r="B191" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" t="s">
-        <v>874</v>
-      </c>
-      <c r="B192" t="s">
-        <v>875</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A62C1B7-928E-4F29-88BD-9E7DDC434D58}">
-  <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>749</v>
-      </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="3"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>841</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4" t="s">
-        <v>848</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>857</v>
-      </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>843</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4" t="s">
-        <v>850</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>859</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>787</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>817</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4" t="s">
-        <v>852</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>989</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
-        <v>818</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>819</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4" t="s">
-        <v>854</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>991</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>734</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>815</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4" t="s">
-        <v>856</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>822</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>823</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>858</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>1039</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>795</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
-        <v>824</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>825</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>860</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>1069</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
-        <v>826</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>827</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>862</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>1071</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>833</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>876</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>835</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>878</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>753</v>
+        <v>737</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>828</v>
+        <v>792</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>845</v>
+        <v>809</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>864</v>
+        <v>824</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>865</v>
+        <v>825</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>830</v>
+        <v>794</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>847</v>
+        <v>811</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>866</v>
+        <v>826</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>867</v>
+        <v>827</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>738</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>781</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>751</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
-        <v>832</v>
+        <v>796</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>965</v>
+        <v>920</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>868</v>
+        <v>828</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>869</v>
+        <v>829</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>834</v>
+        <v>798</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>967</v>
+        <v>921</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>870</v>
+        <v>830</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>871</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>739</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>759</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>752</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>836</v>
+        <v>800</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>889</v>
+        <v>847</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>872</v>
+        <v>832</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>873</v>
+        <v>833</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>891</v>
+        <v>849</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>874</v>
+        <v>834</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>875</v>
+        <v>835</v>
       </c>
     </row>
   </sheetData>
@@ -8470,183 +6483,708 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2872A1D-07A2-4177-95D4-1AF2F854DE62}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>760</v>
+        <v>743</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>773</v>
+        <v>756</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>884</v>
+        <v>842</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>893</v>
+        <v>851</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>904</v>
+        <v>862</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>933</v>
+        <v>891</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>886</v>
+        <v>844</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>895</v>
+        <v>853</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>906</v>
+        <v>864</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>935</v>
+        <v>893</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>758</v>
+        <v>741</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>794</v>
+        <v>769</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>892</v>
+        <v>850</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>885</v>
+        <v>843</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>896</v>
+        <v>854</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1065</v>
+        <v>960</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>894</v>
+        <v>852</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>887</v>
+        <v>845</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>898</v>
+        <v>856</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1067</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>764</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>880</v>
+        <v>838</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>837</v>
+        <v>801</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>908</v>
+        <v>866</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>909</v>
+        <v>867</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>882</v>
+        <v>840</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>839</v>
+        <v>803</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>910</v>
+        <v>868</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>911</v>
+        <v>869</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>769</v>
+        <v>752</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>762</v>
+        <v>745</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>888</v>
+        <v>846</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>921</v>
+        <v>879</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>900</v>
+        <v>858</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>901</v>
+        <v>859</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>861</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6613AC13-ACCE-4AA0-A63E-04D9E0B67E63}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>890</v>
       </c>
+      <c r="E5" s="4" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>876</v>
+      </c>
       <c r="B12" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>889</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A70F0A5-D008-4ED4-8AF5-C5B22A4C9F9B}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="15.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E3" s="4" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
         <v>902</v>
       </c>
+      <c r="B8" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>928</v>
+      </c>
       <c r="E12" s="4" t="s">
-        <v>903</v>
+        <v>953</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D60361-1E8F-423A-BC25-BF117E379490}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>949</v>
       </c>
     </row>
   </sheetData>
